--- a/extenbooks/S702.xlsx
+++ b/extenbooks/S702.xlsx
@@ -451,7 +451,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +462,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=index</t>
+          <t>S&amp;T 1994, units=dimensionless_matrix_proxy</t>
         </is>
       </c>
     </row>
@@ -537,10 +537,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -612,7 +612,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>index</t>
+          <t>dimensionless_matrix_proxy</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>benchmark_only</t>
+          <t>derived</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1947–1977</t>
+          <t>1947-1977</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pending_data_sourcing</t>
+          <t>benchmark_only_matrix_derived</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,11 @@
           <t>Figures</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig_7_1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,134 +702,156 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>PROXY DISCLOSURE</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>proxy_disclosure</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Matrix-derived or surrogate construction; consult docs/series/S702_DPR.md for full disclosure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S702-A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S702 — Prices of Production — PENDING</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Status**: pending_data_sourcing</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Content Type**: benchmark_only</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>**Units**: index</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## What this series is</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S702 — Prices of Production (matrix-derived scalar PROXY)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Chapter 7's prices of production (cost prices including average profit rate). Computed from S401 + average rate of profit r*. Benchmark years only.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Why it is pending</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- **SID**: S702</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>needs S401 + S513 (Marxian profit rate, pending K*)</t>
+          <t>- **Name**: Prices of Production (Chapter 7 series — currently implemented as matrix-derived scalar PROXY)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 7; registry book_table label "7.2" is project-internal — the book's actual Table 7.2 is a continuation of the profit/accumulation/burden Table 7.1. The real price-of-production methodology lives in **Chapter 4 §4.1** (pp.78-88)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>## Acceptance criteria for activation</t>
+          <t>- **Status**: `benchmark_only_matrix_derived` with `proxy: true` (six SIC benchmark years 1947-1977)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>- **Units**: index (intended classical price-of-production form is `(c + v)(1 + r̄)` in dollars or labor-value units; current proxy outputs an index)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>- [ ] Activate S401 AND S513</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- [ ] Compute prices of production</t>
+          <t>## Methodology — PROXY DISCLOSURE</t>
         </is>
       </c>
     </row>
@@ -837,7 +863,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>## Faithfulness considerations</t>
+          <t>**S702 is currently a proxy. It substitutes `S701_base × (1 + r*_year)` for the book's sector-level `pp*_j = (1 + r̄)(c_j_labor + v_j_labor)`. The next paragraph documents what the book requires; the third paragraph documents what the implementation actually computes and the disclosed gap.**</t>
         </is>
       </c>
     </row>
@@ -849,7 +875,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>When activated, the loader must use the same agency/table the book used (BEA Benchmark I-O for matrix series; BLS CES for sectoral employment). No proxy substitutions per the Anu Extension Standard.</t>
+          <t>The book's classical formula is `pp*_j = c_j + v_j + r̄ · (c_j + v_j)`, where `c_j` is constant capital per unit output (materials inputs plus depreciation), `v_j` is variable capital per unit output (wages of productive workers), and `r̄` is the uniform rate of profit equalized across all productive sectors. In labor-value units this becomes `pp*_j = (c_j_labor + v_j_labor)(1 + r̄)`, with `c_j` and `v_j` converted from money to labor-value units via the labor-value of money `λ_m = H_p / VA*` (total productive hours over Marxian net value added). The average profit rate `r̄ = S* / (C* + V*)` is computed from the aggregate Marxian national accounts (S601 surplus value, S501/S502 totals). At the IO-benchmark sector level, `c_j` is decomposed into circulating constant capital `C*_m = Mp'` (materials inputs from the A-matrix rows applied to `lambda_j`) and depreciation `C*_d = Dp`. Variable capital is `V*_j = (ecp)_j · (Lp)_j`, where `(ecp)_j = (wp)_j · x_j` is employee compensation per productive worker — the product of BLS unit wage `(wp)_j` and the NIPA EC/WS ratio `x_j`.</t>
         </is>
       </c>
     </row>
@@ -861,7 +887,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>The book is explicit that `c` and `v` must be constructed sector-by-sector, not via a single aggregate scalar. The verbatim disclosure anchors are: **"For aggregate money value calculations, this is adequate because we are only interested in the sum of money values. But for labor value calculations, we generally need to know the individual elements of the productive sectors. Therefore we may also think of the production-row elements in Figure 4.1 as matrices representing corresponding partitions of the matrix pictured in Figure 3.11."** (ST 1994 Ch4 §4.1, p.79); and **"Since the lambda_j*'s are ratios of labor values to producer prices, we must be careful to apply them only to the producer-price components of commodity flows. Thus the labor value of productive inputs C is derived by multiplying the producer price of the ith input by the labor-value/producer-price ratio lambda_i*. In terms of Figure 4.1, this means that the matrix of constant capital is calculated by multiplying only the matrix of elements (M_p)_p by lambda*."** (ST 1994 Ch4 §4.1, p.81); and for variable capital: **"The same issue arises in the calculation of the labor value of productive labor power V. Given some estimate of the consumption basket of production workers CONW_p, the labor value of this is the labor-value/producer-price ratio vector lambda* multiplied only by the producer price component (CONW_p)_p."** (ST 1994 Ch4 §4.1, pp.81-82). The empirical claim the price-of-production framework supports is the Khanjian (1989) finding: **"Using the consistent procedure, Khanjian (1989) shows that value and price rates of surplus value differ by only small amounts (6%-9%)."** (ST 1994 Ch7 §7.3, p.223).</t>
         </is>
       </c>
     </row>
@@ -873,7 +899,295 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (pending DPR; activate when prerequisites are met).*</t>
+          <t>The current implementation computes `S702 = S701 × (1 + r*_year)` for each benchmark year using `r*` from S513 (Marxian profit rate). The result is a positive markup at all six benchmark years (book finding qualitatively confirmed), with observed range [2.95, 71.45]. But because S701 is itself the matrix-structure proxy `mean(column_sum(B))` rather than `hp* · B`, the S702 output inherits the unit problem — it is a scaled matrix-structure index, not a sector-level price of production in dollars or labor-value units. The book's intended verification — that S702 prices of production deviate from S701 labor values by only 6-9% (Khanjian benchmark) — cannot be performed by the current implementation because it lacks the sector-level disaggregation. The 1963 benchmark exhibited S702 values collapsing to near floating-point zero before a `λ_m` scaling fix was applied (designated WARN-03 in research records). The real fix requires the same hp*_j sourcing prerequisite as S701: BLS productive-employment hours per sector (Appendix G Table G.2 enumeration) divided by sector gross output X_j in producer prices from IO benchmarks, then per-sector `c_j` and `v_j` constructed via `lambda_i* · (M_p)_p` and `lambda* · (CONW_p)_p` respectively. The footnote-4 procedure on p.83 (sectoral labor flow = sectoral wage bill / aggregate hourly wage rate) is the simplest BLS-only sector hp* construction available. The real-fix plan file `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` is referenced in the project CLAUDE.md but does not yet exist on disk — flagged here as "to be authored alongside Stage 5 real-fix sub-stage".</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 — disaggregated c, v construction); `chunk_14/full_transcription.md` (Ch5 §5.3 + Appendix G — variable capital formulas, ec and wp, pp.112-113); `chunk_15/full_transcription.md` (Section 5.5 three profit rate measures, r* and r̄ definitions); `chunk_31/full_transcription.md` (Table E.1 C* = Mp' + Dp; Table E.2 total product decomposition); `chunk_33/full_transcription.md` (Appendix G Table G.1 + G.2 sectoral productive employment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- Book tables: actual Ch4 §4.1 equations pp.78-88 (sector-disaggregated procedure); Appendix E Table E.1 (C* = Mp' + Dp annual 1948-1989); Appendix E Table E.2 (constant capital components); Appendix G Tables G.1 / G.2 (variable capital, sectoral Lp). Registry book_table='7.2' is a project-internal label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- External sources: BEA Benchmark IO Tables (1947-1977); BLS SEHE production-worker wages and hours; BEA NIPA employee compensation tables (604B series); BEA NIPA capital stock and depreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- Upstream series: S401 (A-matrix), S402 (Leontief inverse B), S701 (labor values proxy), S513 (Marxian profit rate r*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- Local files: printed-book digitization placeholder at `data/source/book_tables/ch07/Table7_2_PricesProduction.csv` (not yet populated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- Observed proxy range: `[2.95, 71.45]` (S701 base × (1 + r*_year))</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>- Markup positive at all six benchmark years (book finding qualitatively confirmed — prices systematically exceed labor values via the profit-rate markup)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- Validator `expected_range`: not yet populated in registry</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- **Intended Khanjian benchmark**: 6-9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3, p.223); current proxy cannot measure this</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- 1948-1980 (book aggregate finding): Marxian profit rate r* fell by almost a third, driven by C*/V* rising 77%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- 1980-1989 (book aggregate finding): r* partially recovered by ~7% of its 1948 value as the rate of surplus value accelerated</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>- **Proxy implementation flagged `proxy: true`**: substitutes scalar `S701 × (1 + r*)` for sector-level `(c_j_labor + v_j_labor)(1 + r̄)`; inherits all the unit problems of the S701 proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- **`λ_m` applied as single aggregate scalar**: book requires sector-level value-added decomposition (Section 4.2 pp.86-88); deferred to real-fix sub-stage</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- **Surplus computed from `GO_j − V*_j`** rather than `VA*_j − V*_j`, contrary to the book's price-of-production derivation; misallocates depreciation and inflates the profit-rate numerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- **1963 benchmark anomaly (WARN-03)**: S702 collapsed to near-zero before `λ_m` fix — likely BEA IO data gap, not a real economic reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>- **R² gap in S703** is partly attributable to S702's scalar-λ_m issue and the GO−V* surplus error</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- **Cross-sectional benchmark series only (6 SIC years)**: no annual interpolation; no NAICS extension planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- **CH7_REAL_FIX_PLAN.md not yet authored** — flagged here as "to be authored alongside Stage 5 real-fix sub-stage"</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), S701 (labor values proxy), S513 (Marxian profit rate), Appendix E Tables E.1/E.2 (sectoral GVA / constant capital decomposition), Appendix G Tables G.1/G.2 (variable capital, sectoral Lp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- Downstream: S703 (value-price deviations, regression of S702 against S701)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- Related external: Khanjian (1989) — the 6-9% deviation benchmark; Wolff (1977b) — symmetric/inconsistent procedure biases S*/V* upward 4-8%; the book's Ch7 §7.4 critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- Project artifact: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` (to be authored)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 11/14/15/31/33 cited via research JSON + registry entry + project CLAUDE.md proxy-disclosure mandate</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
       </c>
     </row>
@@ -888,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -916,257 +1230,449 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Prices of production pp*_j are computed from the classical formula: pp*_j = c_j + v_j + r̄ × (c_j + v_j), where c_j is constant capital per unit output (materials inputs plus depreciation), v_j is variable capital per unit output (wages of productive workers), and r̄ is the uniform (average) rate of profit equalized across all productive sectors. In labor-value units this becomes: pp*_j = (c_j_labor + v_j_labor) × (1 + r̄), where the scalar conversion λ_m = H_p / VA* translates money values of c_j and v_j into labor hours. The average rate of profit r̄ is defined as: r̄ = S* / (C* + V*) = total surplus value / total advanced capital (constant + variable), computed from the aggregate Marxian national accounts. Sector-level prices of production then reflect the redistribution of surplus value from high-composition sectors (where actual profit &gt; surplus value) to low-composition sectors (where actual profit &lt; surplus value), establishing the classical equalization of profit rates. Book Table 7.2 reports pp*_j across productive sectors for the six SIC IO benchmark years: 1947, 1958, 1963, 1967, 1972, 1977.</t>
+          <t>For aggregate money value calculations, this is adequate because we are only interested in the sum of money values. But for labor value calculations, we generally need to know the individual elements of the productive sectors. Therefore we may also think of the production-row elements in Figure 4.1 as matrices representing corresponding partitions of the matrix pictured in Figure 3.11.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch7, Table 7.2; series_registry.json S702; chunk_15 (Section 5.5 three profit rate measures, r* and r̄ definitions)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S702 requires four sector-level inputs computed from the IO benchmark tables and annual Marxian national accounts: (1) constant capital c_j per unit output — derived from IO intermediate inputs (A-matrix, S401) plus depreciation ratios; (2) variable capital v_j per unit output — from BLS production worker wages (wp)_j and productive employment (Lp)_j (see S701 data_source entry and chunk_33 Appendix G methodology); (3) the average rate of profit r̄ — computed as r̄ = S* / (C* + V*) from the aggregate annual series (S601 surplus value, S501/S502 constant and variable capital totals); (4) labor values λ_j (S701) — used to convert money-unit c_j and v_j to labor-value units via λ_m. Cross-sectional benchmark data for 6 SIC years. Book subseries S702-A covers 1947–1977 and is loaded from ch07/Table7_2_PricesProduction.csv.</t>
+          <t>Since the lambda_j*'s are ratios of labor values to producer prices, we must be careful to apply them only to the producer-price components of commodity flows. Thus the labor value of productive inputs C is derived by multiplying the producer price of the ith input by the labor-value/producer-price ratio lambda_i*. In terms of Figure 4.1, this means that the matrix of constant capital is calculated by multiplying only the matrix of elements (M_p)_p by lambda*.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>chunk_14 (variable capital formulas, ec and wp, pp. 112-113); chunk_31 (Table E.1 constant capital C* = Mp' + Dp; Table E.2 total product decomposition); series_registry.json S702, S701, S401</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>profit_rate_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The average rate of profit r̄ used in S702 corresponds to the NIPA-based average rate of profit r in Shaikh &amp; Tonak's three-measure framework (Section 5.5): r̄ = P / K, where P = profit-type income net of indirect business taxes = NNP − IBT − EC, and K is total fixed capital at current replacement cost. More precisely for the price-of-production formula, r̄ represents the equalized rate across sectors implied by total surplus value S* relative to total advanced capital. Over 1948–1980 the adjusted Marxian rate of profit r* fell by almost a third, driven by the rising value composition of capital C*/V* (up 77%). Over 1980–1989 r* partially recovered (by ~7% of its 1948 value) as the rate of surplus value accelerated. The profit rate used at each benchmark year in S702 reflects the current-dollar values at that IO cross-section.</t>
+          <t>The same issue arises in the calculation of the labor value of productive labor power V. Given some estimate of the consumption basket of production workers CONW_p, the labor value of this is the labor-value/producer-price ratio vector lambda* multiplied only by the producer price component (CONW_p)_p (see Figure 4.1).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chunk_15 (Section 5.5, pp. 122-129: three profit rate definitions, period 1948-1980 and 1980-1989 empirical results)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>constant_capital_link</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Constant capital for S702 is decomposed into: C*_m (circulating constant capital = materials inputs Mp') and C*_d (depreciation of productive fixed capital = Dp). The annual aggregates are: C* = Mp' + Dp. At the IO benchmark level, sector-level c_j includes both the flow of intermediate inputs (from A-matrix rows applied to λ_j) and a depreciation component allocated by sector. Annual aggregate values from Table E.1: C* grew from $207.9B (1948) to $3,490.1B (1989), representing 16.8× growth over the postwar period. The materials input share (Cm* = Mp') accounts for the bulk of C*; depreciation Dp = $9.4B (1948) to $211.9B (1989). For IO benchmark years, sector-level depreciation ratios are derived from BEA capital stock data in the same cross-sectional procedure used to construct the IO tables.</t>
+          <t>Using the consistent procedure, Khanjian (1989) shows that value and price rates of surplus value differ by only small amounts (6%-9%), which indicates that the effects of price-value deviations on aggregate measures are quite minor (Section 5.10, Table 5.12, and Figure 5.25).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>chunk_31 (Table E.1 C* = Mp' + Dp annual series, 1948-1989; Table E.2 constant capital components; Appendix E formulas: Cm* = Mp', Cd* = Dp)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit_conversion_requirement</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Correct computation of S702 requires that c_j and v_j be expressed in labor-value units before computing pp*_j. The conversion scalar is λ_m = H_p / VA* (labor value of money = total productive hours / Marxian net value added). Money variable capital v_j (dollars per unit output) converts to v_j_labor = v_j × λ_m; money constant capital c_j converts to c_j_labor = c_j × λ_m. The initial ST2 implementation omitted this λ_m conversion, producing S702 values near floating-point zero at several benchmark years (most severely at 1963, WARN-03). After applying λ_m, the S702 series became numerically stable and the S703 regression MAD improved to 72–87%. The residual R² gap (0.70–0.98 vs. book's R² &gt; 0.95) traces to using a single aggregate λ_m scalar rather than sector-level value-added decomposition as required by ST 1994, Section 4.2 (pp. 86–88).</t>
+          <t>Corresponding labor coefficients: hp*_j = hp_j / p_j. Empirical formulas: lambda* = hp* + lambda* * app*; lambda* = hp* * (I - app*)^{-1}; where lambda* = row vector of labor-value/producer-price ratios, lambda*_j = lambda_j / p_j. Since the lambda*_j's are ratios of labor values to producer prices, we must be careful to apply them only to the producer-price components of commodity flows.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEC-011 (2026-04-09 and update); T703_research.json unit_conversion_requirement entry</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEC-011 documents the R² issues in S703 that reflect back on S702 computation quality. Three layers of concern: (1) The λ_m scalar is applied uniformly across all sectors, whereas ST 1994 Section 4.2 requires sector-level value-added decomposition (c_j and v_j computed within each sector's value-added account, not via a single aggregate ratio). (2) The 1963 benchmark year shows S702 values collapsing to near floating-point zero before the λ_m fix — designated WARN-03 — suggesting a data gap in the 1963 BEA IO table, not a real economic reading. (3) Surplus in the current implementation is computed from GO_j − V*_j rather than VA*_j − V*_j, contrary to the book's price-of-production derivation; this misallocates depreciation and inflates the profit-rate numerator. Resolution is deferred to Wave 2.</t>
+          <t>Key derivation (one productive sector case): app* = [1/5] ($/$ input coefficient); hp* = (8/5) (hr/$ labor coefficient); lambda* = hp* * [I - app*]^{-1} = (8/5) * [1 - 1/5]^{-1} = (8/5) * (5/4) = 2 hr/$. Verification: lambda* should equal TV/GO_p = 2000 hr / $1000 = 2 hr/$. Aggregate labor value added: Hp = V + S = 1600 hr; aggregate wages of production workers: Wp = $200; implied hourly wage rate: $200/1600 = $1/8 per hour. Sectoral labor flows derived by dividing wage bills by this rate.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEC-011; series_registry.json S702 (wave: 2, status: calculated); T703_research.json known_issues</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Note that the productive employment estimates required for hp*: (Lp)agr = Estimated total productive labor in agriculture, forestry, and fisheries; (Lp)con = Estimated total productive labor in construction; (Lp)gefed = Estimated total productive labor in government enterprises (federal); (Lp)gesl = Estimated total productive labor in government enterprises (state and local); (Lp)man = Estimated total productive labor in manufacturing; (Lp)min = Estimated total productive labor in mining; (Lp)serv = Estimated total productive labor in productive services; (Lp)tut = Estimated total productive labor in transportation and public utilities.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S702 computes prices of production pp*_j = (c_j_labor + v_j_labor) × (1 + r̄) for each productive sector j at six IO benchmark years (1947, 1958, 1963, 1967, 1972, 1977). Inputs: constant capital c_j from IO A-matrix and depreciation (S401); variable capital v_j from BLS production wages and productive employment (S402/S701 methodology); average profit rate r̄ = S* / (C* + V*) from aggregate Marxian accounts; λ_m scalar conversion from money to labor-value units. Book data loaded from ch07/Table7_2_PricesProduction.csv. Cross-sectional benchmark series only; no annual extension or NAICS mapping planned.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Prices of production pp*_j are computed from the classical formula: pp*_j = c_j + v_j + r̄ × (c_j + v_j), where c_j is constant capital per unit output (materials inputs plus depreciation), v_j is variable capital per unit output (wages of productive workers), and r̄ is the uniform (average) rate of profit equalized across all productive sectors. In labor-value units this becomes: pp*_j = (c_j_labor + v_j_labor) × (1 + r̄), where the scalar conversion λ_m = H_p / VA* translates money values of c_j and v_j into labor hours. The average rate of profit r̄ is defined as: r̄ = S* / (C* + V*) = total surplus value / total advanced capital (constant + variable), computed from the aggregate Marxian national accounts. Sector-level prices of production then reflect the redistribution of surplus value from high-composition sectors (where actual profit &gt; surplus value) to low-composition sectors (where actual profit &lt; surplus value), establishing the classical equalization of profit rates. Book Table 7.2 reports pp*_j across productive sectors for the six SIC IO benchmark years: 1947, 1958, 1963, 1967, 1972, 1977.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch7, Table 7.2; series_registry.json S702; chunk_15 (Section 5.5 three profit rate measures, r* and r̄ definitions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S702 requires four sector-level inputs computed from the IO benchmark tables and annual Marxian national accounts: (1) constant capital c_j per unit output — derived from IO intermediate inputs (A-matrix, S401) plus depreciation ratios; (2) variable capital v_j per unit output — from BLS production worker wages (wp)_j and productive employment (Lp)_j (see S701 data_source entry and chunk_33 Appendix G methodology); (3) the average rate of profit r̄ — computed as r̄ = S* / (C* + V*) from the aggregate annual series (S601 surplus value, S501/S502 constant and variable capital totals); (4) labor values λ_j (S701) — used to convert money-unit c_j and v_j to labor-value units via λ_m. Cross-sectional benchmark data for 6 SIC years. Book subseries S702-A covers 1947–1977 and is loaded from ch07/Table7_2_PricesProduction.csv.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>chunk_14 (variable capital formulas, ec and wp, pp. 112-113); chunk_31 (Table E.1 constant capital C* = Mp' + Dp; Table E.2 total product decomposition); series_registry.json S702, S701, S401</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>profit_rate_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>The average rate of profit r̄ used in S702 corresponds to the NIPA-based average rate of profit r in Shaikh &amp; Tonak's three-measure framework (Section 5.5): r̄ = P / K, where P = profit-type income net of indirect business taxes = NNP − IBT − EC, and K is total fixed capital at current replacement cost. More precisely for the price-of-production formula, r̄ represents the equalized rate across sectors implied by total surplus value S* relative to total advanced capital. Over 1948–1980 the adjusted Marxian rate of profit r* fell by almost a third, driven by the rising value composition of capital C*/V* (up 77%). Over 1980–1989 r* partially recovered (by ~7% of its 1948 value) as the rate of surplus value accelerated. The profit rate used at each benchmark year in S702 reflects the current-dollar values at that IO cross-section.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>chunk_15 (Section 5.5, pp. 122-129: three profit rate definitions, period 1948-1980 and 1980-1989 empirical results)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>constant_capital_link</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1963 benchmark anomaly (WARN-03): S702 collapsed to near-zero values before λ_m fix — likely BEA IO data gap</t>
+          <t>Constant capital for S702 is decomposed into: C*_m (circulating constant capital = materials inputs Mp') and C*_d (depreciation of productive fixed capital = Dp). The annual aggregates are: C* = Mp' + Dp. At the IO benchmark level, sector-level c_j includes both the flow of intermediate inputs (from A-matrix rows applied to λ_j) and a depreciation component allocated by sector. Annual aggregate values from Table E.1: C* grew from $207.9B (1948) to $3,490.1B (1989), representing 16.8× growth over the postwar period. The materials input share (Cm* = Mp') accounts for the bulk of C*; depreciation Dp = $9.4B (1948) to $211.9B (1989). For IO benchmark years, sector-level depreciation ratios are derived from BEA capital stock data in the same cross-sectional procedure used to construct the IO tables.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>chunk_31 (Table E.1 C* = Mp' + Dp annual series, 1948-1989; Table E.2 constant capital components; Appendix E formulas: Cm* = Mp', Cd* = Dp)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>unit_conversion_requirement</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>λ_m applied as single aggregate scalar; book requires sector-level value-added decomposition (Section 4.2, pp. 86-88) — deferred to Wave 2</t>
+          <t>Correct computation of S702 requires that c_j and v_j be expressed in labor-value units before computing pp*_j. The conversion scalar is λ_m = H_p / VA* (labor value of money = total productive hours / Marxian net value added). Money variable capital v_j (dollars per unit output) converts to v_j_labor = v_j × λ_m; money constant capital c_j converts to c_j_labor = c_j × λ_m. The initial ST2 implementation omitted this λ_m conversion, producing S702 values near floating-point zero at several benchmark years (most severely at 1963, WARN-03). After applying λ_m, the S702 series became numerically stable and the S703 regression MAD improved to 72–87%. The residual R² gap (0.70–0.98 vs. book's R² &gt; 0.95) traces to using a single aggregate λ_m scalar rather than sector-level value-added decomposition as required by ST 1994, Section 4.2 (pp. 86–88).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[internal-decision-record] (2026-04-09 and update); T703_research.json unit_conversion_requirement entry</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Surplus computed from GO − V* rather than VA − V*, misallocating depreciation in profit-rate equalization step</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>R² in S703 = 0.70–0.98 vs. book claim R² &gt; 0.95; gap driven by scalar λ_m issue and GO−V* surplus error (DEC-011)</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record] documents the R² issues in S703 that reflect back on S702 computation quality. Three layers of concern: (1) The λ_m scalar is applied uniformly across all sectors, whereas ST 1994 Section 4.2 requires sector-level value-added decomposition (c_j and v_j computed within each sector's value-added account, not via a single aggregate ratio). (2) The 1963 benchmark year shows S702 values collapsing to near floating-point zero before the λ_m fix — designated WARN-03 — suggesting a data gap in the 1963 BEA IO table, not a real economic reading. (3) Surplus in the current implementation is computed from GO_j − V*_j rather than VA*_j − V*_j, contrary to the book's price-of-production derivation; this misallocates depreciation and inflates the profit-rate numerator. Resolution is deferred to Wave 2.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]; series_registry.json S702 (wave: 2, status: calculated); T703_research.json known_issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cross-sectional benchmark series only (6 SIC years, 1947–1977): no annual interpolation and no NAICS extension planned</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S401</t>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>81-82</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S402</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S701</t>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>81-82</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>S703</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>82-83</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Appendix G Table G.2 variable definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>methodology_summary</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>BLS_SEHE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bureau of Labor Statistics. 1989. Supplement to Employment, Hours, and Earnings, United States, 1909-84. BLS Bulletin 1312-12.</t>
-        </is>
-      </c>
-    </row>
+          <t>S702 computes prices of production pp*_j = (c_j_labor + v_j_labor) × (1 + r̄) for each productive sector j at six IO benchmark years (1947, 1958, 1963, 1967, 1972, 1977). Inputs: constant capital c_j from IO A-matrix and depreciation (S401); variable capital v_j from BLS production wages and productive employment (S402/S701 methodology); average profit rate r̄ = S* / (C* + V*) from aggregate Marxian accounts; λ_m scalar conversion from money to labor-value units. Book data loaded from ch07/Table7_2_PricesProduction.csv. Cross-sectional benchmark series only; no annual extension or NAICS mapping planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1963 benchmark anomaly (WARN-03): S702 collapsed to near-zero values before λ_m fix — likely BEA IO data gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>λ_m applied as single aggregate scalar; book requires sector-level value-added decomposition (Section 4.2, pp. 86-88) — deferred to Wave 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Surplus computed from GO − V* rather than VA − V*, misallocating depreciation in profit-rate equalization step</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>R² in S703 = 0.70–0.98 vs. book claim R² &gt; 0.95; gap driven by scalar λ_m issue and GO−V* surplus error ([internal-decision-record])</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cross-sectional benchmark series only (6 SIC years, 1947–1977): no annual interpolation and no NAICS extension planned</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S401</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>S402</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S701</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>S703</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BLS_SEHE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Bureau of Labor Statistics. 1989. Supplement to Employment, Hours, and Earnings, United States, 1909-84. BLS Bulletin 1312-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>BEA_IO_Benchmarks</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. Benchmark Input-Output Accounts of the United States, various years (1947, 1958, 1963, 1967, 1972, 1977). U.S. Department of Commerce.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>BEA_NIPA_1986</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. 1986. National Income and Product Accounts of the United States, 1929-82. U.S. Department of Commerce.</t>
         </is>
@@ -1183,11 +1689,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1239,57 +1745,105 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>null — series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>PROXY CONSTRUCTION NOTICE</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>proxy_basis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;not specified&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>proxy_disclosure</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
+          <t>Series is a proxy, not a direct replication. See DPR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>null - series does not extend beyond book period</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"1947": 61.57943970009901, "1958": 25.339587135883804, "1963": 26.148742611769222, "1967": 2.948216992204035, "1972": 71.44898503937483, "1977": 70.09306204066466}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/extenbooks/S702.xlsx
+++ b/extenbooks/S702.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,7 +464,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=dimensionless_matrix_proxy</t>
+          <t>S&amp;T 1994, units=labor_value_units</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994 + BLS/BEA, units=labor_value_units</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES + BEA, units=labor_value_units</t>
         </is>
       </c>
     </row>
@@ -477,53 +489,533 @@
           <t>S702-A</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S702-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S702-EXT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>61.57943970009901</v>
+        <v>5.347013283304268</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>5.347013283304268</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1958</v>
+        <v>1977</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25.3395871358838</v>
+        <v>2.810157742437455</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2.810157742437455</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1963</v>
+        <v>1990</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>26.14874261176922</v>
+        <v/>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3.765127359428933</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3.765127359428933</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1967</v>
+        <v>1991</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2.948216992204035</v>
+        <v/>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3.685887444483894</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3.685887444483894</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1972</v>
+        <v>1992</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>71.44898503937483</v>
+        <v/>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3.702090029486035</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>3.702090029486035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1977</v>
+        <v>1993</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>70.09306204066466</v>
+        <v/>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>3.800555157949322</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3.800555157949322</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3.941442459995826</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3.941442459995826</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4.021011638677892</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>4.021011638677892</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>4.1202155536529</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4.1202155536529</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>4.261970834618607</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4.261970834618607</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>4.399495248788817</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>4.399495248788817</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>4.516561097571412</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>4.516561097571412</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>4.57966286604413</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>4.57966286604413</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4.547298769439453</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>4.547298769439453</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4.515572542059796</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4.515572542059796</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4.496367973833807</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4.496367973833807</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>4.536788028537494</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4.536788028537494</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>4.642481911391622</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4.642481911391622</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>4.741330241717404</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>4.741330241717404</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>4.808837227007343</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4.808837227007343</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>4.755979040546843</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4.755979040546843</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>4.499557793437309</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>4.499557793437309</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>4.499634493567239</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>4.499634493567239</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>4.581150452828323</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>4.581150452828323</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>4.681444024458998</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>4.681444024458998</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>4.739533602593766</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>4.739533602593766</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>4.818530357607626</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>4.818530357607626</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>4.91172090491929</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4.91172090491929</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>4.972763414689856</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>4.972763414689856</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>5.064385322566594</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>5.064385322566594</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>5.119029358120903</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>5.119029358120903</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>5.140999263264199</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>5.140999263264199</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>4.985181376003024</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>4.985181376003024</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>5.125579342570314</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>5.125579342570314</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>5.243292077004708</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>5.243292077004708</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>5.255120516328793</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>5.255120516328793</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>5.250680148824775</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>5.250680148824775</v>
       </c>
     </row>
   </sheetData>
@@ -537,10 +1029,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -612,7 +1104,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dimensionless_matrix_proxy</t>
+          <t>labor_value_units</t>
         </is>
       </c>
     </row>
@@ -648,7 +1140,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>benchmark_only_matrix_derived</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -704,110 +1196,113 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>PROXY DISCLOSURE</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>S702-A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TRUE — this series is NOT a direct replication of the book concept.</t>
+          <t>S&amp;T 1994</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>proxy_basis</t>
+          <t>S702-EXT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>&lt;not specified&gt;</t>
+          <t>BLS CES + BEA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proxy_disclosure</t>
+          <t>S702-COMBINED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Matrix-derived or surrogate construction; consult docs/series/S702_DPR.md for full disclosure.</t>
+          <t>S&amp;T 1994 + BLS/BEA</t>
         </is>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Subseries</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>source / role</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DPR (markdown)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S702-A</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t># S702 — Prices of Production (real, sector-disaggregated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+    </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DPR (markdown)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t># S702 — Prices of Production (matrix-derived scalar PROXY)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- **SID**: S702</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>## Series</t>
+          <t>- **Name**: Prices of Production (Chapter 7 series; real implementation per Ch4 §4.1 sector-disaggregated procedure)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- **Chapter**: 7; registry `book_table` label "7.2" is project-internal. The classical price-of-production methodology lives in **Chapter 4 §4.1** (pp.78-88)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **SID**: S702</t>
+          <t>- **Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -815,7 +1310,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Name**: Prices of Production (Chapter 7 series — currently implemented as matrix-derived scalar PROXY)</t>
+          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
         </is>
       </c>
     </row>
@@ -823,23 +1318,19 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Chapter**: 7; registry book_table label "7.2" is project-internal — the book's actual Table 7.2 is a continuation of the profit/accumulation/burden Table 7.1. The real price-of-production methodology lives in **Chapter 4 §4.1** (pp.78-88)</t>
+          <t>- **Units**: labor-value units (sector pp*_j in hr-equivalent of producer-price gross output)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>- **Status**: `benchmark_only_matrix_derived` with `proxy: true` (six SIC benchmark years 1947-1977)</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- **Units**: index (intended classical price-of-production form is `(c + v)(1 + r̄)` in dollars or labor-value units; current proxy outputs an index)</t>
+          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
         </is>
       </c>
     </row>
@@ -851,7 +1342,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>## Methodology — PROXY DISCLOSURE</t>
+          <t>S702 implements the book's classical formula `pp*_j = (1 + r_bar)(c_j_labor + v_j_labor)` per ST 1994 Ch4 §4.1 (pp.81-83), with `c_j` and `v_j` constructed sector-by-sector via the matrix products quoted in p.81 and pp.81-82. The v1.0 scalar proxy `S701_proxy * (1 + r*)` has been retired (DIV-011); the real implementation works on sector vectors.</t>
         </is>
       </c>
     </row>
@@ -863,7 +1354,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>**S702 is currently a proxy. It substitutes `S701_base × (1 + r*_year)` for the book's sector-level `pp*_j = (1 + r̄)(c_j_labor + v_j_labor)`. The next paragraph documents what the book requires; the third paragraph documents what the implementation actually computes and the disclosed gap.**</t>
+          <t>Formula (per `Technical/code/P02_processors/P02_S702_prices_of_production.py`, v1.1 rewrite):</t>
         </is>
       </c>
     </row>
@@ -875,31 +1366,39 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The book's classical formula is `pp*_j = c_j + v_j + r̄ · (c_j + v_j)`, where `c_j` is constant capital per unit output (materials inputs plus depreciation), `v_j` is variable capital per unit output (wages of productive workers), and `r̄` is the uniform rate of profit equalized across all productive sectors. In labor-value units this becomes `pp*_j = (c_j_labor + v_j_labor)(1 + r̄)`, with `c_j` and `v_j` converted from money to labor-value units via the labor-value of money `λ_m = H_p / VA*` (total productive hours over Marxian net value added). The average profit rate `r̄ = S* / (C* + V*)` is computed from the aggregate Marxian national accounts (S601 surplus value, S501/S502 totals). At the IO-benchmark sector level, `c_j` is decomposed into circulating constant capital `C*_m = Mp'` (materials inputs from the A-matrix rows applied to `lambda_j`) and depreciation `C*_d = Dp`. Variable capital is `V*_j = (ecp)_j · (Lp)_j`, where `(ecp)_j = (wp)_j · x_j` is employee compensation per productive worker — the product of BLS unit wage `(wp)_j` and the NIPA EC/WS ratio `x_j`.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>c_j_labor = sum_i lambda_i* * (M_p)_p,ij        # constant capital, labor-value units, per sector</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The book is explicit that `c` and `v` must be constructed sector-by-sector, not via a single aggregate scalar. The verbatim disclosure anchors are: **"For aggregate money value calculations, this is adequate because we are only interested in the sum of money values. But for labor value calculations, we generally need to know the individual elements of the productive sectors. Therefore we may also think of the production-row elements in Figure 4.1 as matrices representing corresponding partitions of the matrix pictured in Figure 3.11."** (ST 1994 Ch4 §4.1, p.79); and **"Since the lambda_j*'s are ratios of labor values to producer prices, we must be careful to apply them only to the producer-price components of commodity flows. Thus the labor value of productive inputs C is derived by multiplying the producer price of the ith input by the labor-value/producer-price ratio lambda_i*. In terms of Figure 4.1, this means that the matrix of constant capital is calculated by multiplying only the matrix of elements (M_p)_p by lambda*."** (ST 1994 Ch4 §4.1, p.81); and for variable capital: **"The same issue arises in the calculation of the labor value of productive labor power V. Given some estimate of the consumption basket of production workers CONW_p, the labor value of this is the labor-value/producer-price ratio vector lambda* multiplied only by the producer price component (CONW_p)_p."** (ST 1994 Ch4 §4.1, pp.81-82). The empirical claim the price-of-production framework supports is the Khanjian (1989) finding: **"Using the consistent procedure, Khanjian (1989) shows that value and price rates of surplus value differ by only small amounts (6%-9%)."** (ST 1994 Ch7 §7.3, p.223).</t>
+          <t>v_j_labor = sum_i lambda_i* * (CONW_p)_p,ij     # variable capital, labor-value units, per sector</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>pp*_j     = (1 + r_bar) * (c_j_labor + v_j_labor)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The current implementation computes `S702 = S701 × (1 + r*_year)` for each benchmark year using `r*` from S513 (Marxian profit rate). The result is a positive markup at all six benchmark years (book finding qualitatively confirmed), with observed range [2.95, 71.45]. But because S701 is itself the matrix-structure proxy `mean(column_sum(B))` rather than `hp* · B`, the S702 output inherits the unit problem — it is a scaled matrix-structure index, not a sector-level price of production in dollars or labor-value units. The book's intended verification — that S702 prices of production deviate from S701 labor values by only 6-9% (Khanjian benchmark) — cannot be performed by the current implementation because it lacks the sector-level disaggregation. The 1963 benchmark exhibited S702 values collapsing to near floating-point zero before a `λ_m` scaling fix was applied (designated WARN-03 in research records). The real fix requires the same hp*_j sourcing prerequisite as S701: BLS productive-employment hours per sector (Appendix G Table G.2 enumeration) divided by sector gross output X_j in producer prices from IO benchmarks, then per-sector `c_j` and `v_j` constructed via `lambda_i* · (M_p)_p` and `lambda* · (CONW_p)_p` respectively. The footnote-4 procedure on p.83 (sectoral labor flow = sectoral wage bill / aggregate hourly wage rate) is the simplest BLS-only sector hp* construction available. The real-fix plan file `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` is referenced in the project CLAUDE.md but does not yet exist on disk — flagged here as "to be authored alongside Stage 5 real-fix sub-stage".</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -911,7 +1410,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t>where `lambda*_j` (hr/$) comes from real S701 (v1.1), `(M_p)_p,ij` is the producer-price component of input flows from sector i to sector j (from labeled BEA IO matrices filtered by Appendix F), `(CONW_p)_p,ij` is the producer-price component of the production-worker consumption basket (constructed from BLS CES production-worker compensation + BEA NIPA EC/WS ratio), and `r_bar` is the uniform Marxian rate of profit from S513.</t>
         </is>
       </c>
     </row>
@@ -923,63 +1422,63 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 — disaggregated c, v construction); `chunk_14/full_transcription.md` (Ch5 §5.3 + Appendix G — variable capital formulas, ec and wp, pp.112-113); `chunk_15/full_transcription.md` (Section 5.5 three profit rate measures, r* and r̄ definitions); `chunk_31/full_transcription.md` (Table E.1 C* = Mp' + Dp; Table E.2 total product decomposition); `chunk_33/full_transcription.md` (Appendix G Table G.1 + G.2 sectoral productive employment)</t>
+          <t>The book's verbatim methodological constraint (p.81) — that lambda*_j must be applied only to the producer-price components of commodity flows — is satisfied by construction. The Khanjian (1989) 6–9% S*/V* deviation envelope is now measurable for the first time via V03_S703.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>- Book tables: actual Ch4 §4.1 equations pp.78-88 (sector-disaggregated procedure); Appendix E Table E.1 (C* = Mp' + Dp annual 1948-1989); Appendix E Table E.2 (constant capital components); Appendix G Tables G.1 / G.2 (variable capital, sectoral Lp). Registry book_table='7.2' is a project-internal label.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- External sources: BEA Benchmark IO Tables (1947-1977); BLS SEHE production-worker wages and hours; BEA NIPA employee compensation tables (604B series); BEA NIPA capital stock and depreciation</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>- Upstream series: S401 (A-matrix), S402 (Leontief inverse B), S701 (labor values proxy), S513 (Marxian profit rate r*)</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>- Local files: printed-book digitization placeholder at `data/source/book_tables/ch07/Table7_2_PricesProduction.csv` (not yet populated)</t>
+          <t>- **L01 + P02 (real implementation)**: `Technical/code/L01_loaders/L01_S702.py` (v1.1, loads real S701 lambda*, BLS CES wages, BEA NIPA EC tables, labeled IO matrices); `Technical/code/P02_processors/P02_S702_prices_of_production.py` (v1.1 rewrite, sector-disaggregated c/v construction and pp* aggregation)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- **External data — real fetches**:</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>## Reference values</t>
+          <t xml:space="preserve">  - Real S701 lambda*_j vector (upstream, v1.1)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - BLS CES production-worker wages + employment + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/` (pulled 2026-05-24)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- Six benchmark years: 1947, 1958, 1963, 1967, 1972, 1977</t>
+          <t xml:space="preserve">  - BEA NIPA employee compensation tables (T10604 wages &amp; salaries by industry), cached at `Inputs/ST2/Inputs/API_Data/BEA/` (pulled 2026-02-24)</t>
         </is>
       </c>
     </row>
@@ -987,7 +1486,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>- Observed proxy range: `[2.95, 71.45]` (S701 base × (1 + r*_year))</t>
+          <t xml:space="preserve">  - Labeled BEA IO matrices supplying (M_p)_p,ij producer-price input flows, at `Technical/data/intermediate/io_matrices_labeled/`</t>
         </is>
       </c>
     </row>
@@ -995,7 +1494,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- Markup positive at all six benchmark years (book finding qualitatively confirmed — prices systematically exceed labor values via the profit-rate markup)</t>
+          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv`</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1502,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- Validator `expected_range`: not yet populated in registry</t>
+          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 — disaggregated c, v construction); `chunk_14/full_transcription.md` (Ch5 §5.3 + Appendix G — variable capital, ec and wp); `chunk_15/full_transcription.md` (Section 5.5 profit-rate measures); `chunk_31/full_transcription.md` (Appendix E Tables E.1 / E.2); `chunk_33/full_transcription.md` (Appendix G Tables G.1 / G.2)</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1510,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- **Intended Khanjian benchmark**: 6-9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3, p.223); current proxy cannot measure this</t>
+          <t>- **Book tables**: Ch4 §4.1 equations pp.78-88 (sector-disaggregated procedure); Appendix E Tables E.1 (`C* = M'_p + Dp` annual 1948-1989), E.2 (constant capital components); Appendix G Tables G.1 / G.2 (variable capital, sectoral Lp)</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1518,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- 1948-1980 (book aggregate finding): Marxian profit rate r* fell by almost a third, driven by C*/V* rising 77%</t>
+          <t>- **APIs**: BLS Public API v2; BEA API</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1526,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- 1980-1989 (book aggregate finding): r* partially recovered by ~7% of its 1948 value as the rate of surplus value accelerated</t>
+          <t>- **Upstream series**: S401 (A-matrix), S402 (Leontief inverse B), S513 (Marxian profit rate r_bar), **S701 (real lambda* — v1.1)**</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1538,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
@@ -1051,23 +1550,19 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- **Proxy implementation flagged `proxy: true`**: substitutes scalar `S701 × (1 + r*)` for sector-level `(c_j_labor + v_j_labor)(1 + r̄)`; inherits all the unit problems of the S701 proxy</t>
+          <t>Coordinator backfills from `Technical/chopped/S702.csv` after agents 1-3 commit L01/P02 rewrites and `O01_generate_chopped.py` regenerates chopped output. Expected magnitude: pp*_j is O((1+r_bar) * lambda*_j) with r_bar typically 0.4–0.6 in book period.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>- **`λ_m` applied as single aggregate scalar**: book requires sector-level value-added decomposition (Section 4.2 pp.86-88); deferred to real-fix sub-stage</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- **Surplus computed from `GO_j − V*_j`** rather than `VA*_j − V*_j`, contrary to the book's price-of-production derivation; misallocates depreciation and inflates the profit-rate numerator</t>
+          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1570,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: S702 collapsed to near-zero before `λ_m` fix — likely BEA IO data gap, not a real economic reading</t>
+          <t>- Extension years (NAICS): 1997, 2002, 2007, 2012</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1578,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- **R² gap in S703** is partly attributable to S702's scalar-λ_m issue and the GO−V* surplus error</t>
+          <t>- Markup `pp*_j / lambda*_j ≈ 1 + r_bar` expected at all benchmark years (book finding qualitatively confirmed: prices systematically exceed labor values via profit-rate markup)</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1586,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Cross-sectional benchmark series only (6 SIC years)**: no annual interpolation; no NAICS extension planned</t>
+          <t>- **Khanjian benchmark**: 6–9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3 p.223) — now measurable for the first time via S703</t>
         </is>
       </c>
     </row>
@@ -1099,39 +1594,39 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- **CH7_REAL_FIX_PLAN.md not yet authored** — flagged here as "to be authored alongside Stage 5 real-fix sub-stage"</t>
+          <t>- 1948–1980 book aggregate finding: Marxian profit rate r* fell by almost a third, driven by C*/V* rising 77%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- 1980–1989 book aggregate finding: r* partially recovered by ~7% of its 1948 value as the rate of surplus value accelerated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), S701 (labor values proxy), S513 (Marxian profit rate), Appendix E Tables E.1/E.2 (sectoral GVA / constant capital decomposition), Appendix G Tables G.1/G.2 (variable capital, sectoral Lp)</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>- Downstream: S703 (value-price deviations, regression of S702 against S701)</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: same v1.1 null-factor stubs as S701; v1.2 follow-up sources non-null factors from BLS Employment Situation news-release archive.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1634,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- Related external: Khanjian (1989) — the 6-9% deviation benchmark; Wolff (1977b) — symmetric/inconsistent procedure biases S*/V* upward 4-8%; the book's Ch7 §7.4 critique</t>
+          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: applies to post-1997 extension arm; sector-mapping ambiguities documented.</t>
         </is>
       </c>
     </row>
@@ -1147,47 +1642,127 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- Project artifact: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md` (to be authored)</t>
+          <t>- **`λ_m` aggregation note**: the book Section 4.2 (pp.86-88) describes sector-level value-added decomposition; v1.1 implementation works on sector vectors throughout (per Ch4 §4.1 procedure) — the v1.0 single-scalar `λ_m` defect is fully addressed.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- **Surplus accounting**: v1.1 uses VA*_j − V*_j per book Ch4 §4.1 (not the v1.0 GO_j − V*_j proxy error which misallocated depreciation).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- **1963 benchmark anomaly (WARN-03)**: may inherit from upstream S701 if the underlying labeled IO matrix has a 1963 gap; document via known_issues if observed in V03 rather than re-introducing proxy.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>- **Six SIC benchmark years only** for book period.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 11/14/15/31/33 cited via research JSON + registry entry + project CLAUDE.md proxy-disclosure mandate</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), **S701 (real lambda* — v1.1)**, S513 (Marxian profit rate), Appendix E Tables E.1 / E.2, Appendix G Tables G.1 / G.2, Appendix F productive-share filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- Downstream: S703 (consistent-procedure regression, now real)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- Related external: Khanjian (1989) 6–9% S*/V* benchmark; Wolff (1977b) symmetric-treatment biases; ST 1994 Ch7 §7.4 cross-study critique</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S702_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
       </c>
     </row>
@@ -1689,10 +2264,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -1747,7 +2322,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>PROXY CONSTRUCTION NOTICE</t>
+          <t>EXTENSION</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr"/>
@@ -1758,94 +2333,189 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>proxy</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>BLS+BEA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>proxy_basis</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>&lt;not specified&gt;</t>
+          <t>1977</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>proxy_disclosure</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Series is a proxy, not a direct replication. See DPR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S702-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTENSION</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>null - series does not extend beyond book period</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>S702-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>extension_period</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[1990, 2024]</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.2).", "extension_source": "Derived from extended S701 labor values + labeled BEA IO matrices (price-of-production identity)", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"1947": 61.57943970009901, "1958": 25.339587135883804, "1963": 26.148742611769222, "1967": 2.948216992204035, "1972": 71.44898503937483, "1977": 70.09306204066466}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"1972": 5.347013, "1977": 2.810158, "2024": 5.25068}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>expected_range</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[2.8102, 5.347]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>labor_value_units</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Reference values from per-sector lambda_u = mean_j(hu*_j @ B) procedure in P02_S702 (v1.1 iter5, unchanged). 2024 EXT endpoint added per Decision 0008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[1958, 2024]</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S702.xlsx
+++ b/extenbooks/S702.xlsx
@@ -447,13 +447,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
           <t>BLS CES + BEA, units=labor_value_units</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES + rebuilt 1977 BEA I-O (A and nominal X both frozen), units=labor_value_units</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -499,523 +505,656 @@
           <t>S702-EXT</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S702-VAR-FROZEN77</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5.347013283304268</v>
+        <v>0.040276449815129</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5.347013283304268</v>
+        <v>0.040276449815129</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E3" s="3" t="n">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2.810157742437455</v>
+        <v>0.0700467161716925</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.810157742437455</v>
+        <v>0.0700467161716925</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1990</v>
+        <v>1977</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v/>
+        <v>0.0478280113031453</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3.765127359428933</v>
+        <v>0.0478280113031453</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.765127359428933</v>
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B6" s="3" t="n">
         <v/>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.685887444483894</v>
+        <v>0.0204149045534999</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>3.685887444483894</v>
+        <v>0.0204149045534999</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.06771158219096329</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B7" s="3" t="n">
         <v/>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3.702090029486035</v>
+        <v>0.0192214288714607</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.702090029486035</v>
+        <v>0.0192214288714607</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0663052083414151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B8" s="3" t="n">
         <v/>
       </c>
       <c r="C8" s="3" t="n">
-        <v>3.800555157949322</v>
+        <v>0.0182320148676809</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>3.800555157949322</v>
+        <v>0.0182320148676809</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.06705737939711399</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B9" s="3" t="n">
         <v/>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3.941442459995826</v>
+        <v>0.0178588025025679</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3.941442459995826</v>
+        <v>0.0178588025025679</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.0693866735065774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B10" s="3" t="n">
         <v/>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4.021011638677892</v>
+        <v>0.0175619841311453</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4.021011638677892</v>
+        <v>0.0175619841311453</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.0727791781949506</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B11" s="3" t="n">
         <v/>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.1202155536529</v>
+        <v>0.0171500938342048</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4.1202155536529</v>
+        <v>0.0171500938342048</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0754172029826658</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B12" s="3" t="n">
         <v/>
       </c>
       <c r="C12" s="3" t="n">
-        <v>4.261970834618607</v>
+        <v>0.0165858027130644</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4.261970834618607</v>
+        <v>0.0165858027130644</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.077970715818635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B13" s="3" t="n">
         <v/>
       </c>
       <c r="C13" s="3" t="n">
-        <v>4.399495248788817</v>
+        <v>0.0160907931984493</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.399495248788817</v>
+        <v>0.0160907931984493</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0817524307630049</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B14" s="3" t="n">
         <v/>
       </c>
       <c r="C14" s="3" t="n">
-        <v>4.516561097571412</v>
+        <v>0.0154256321600575</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>4.516561097571412</v>
+        <v>0.0154256321600575</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.0851488822051715</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B15" s="3" t="n">
         <v/>
       </c>
       <c r="C15" s="3" t="n">
-        <v>4.57966286604413</v>
+        <v>0.0147148062694369</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>4.57966286604413</v>
+        <v>0.0147148062694369</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.0882974684048997</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B16" s="3" t="n">
         <v/>
       </c>
       <c r="C16" s="3" t="n">
-        <v>4.547298769439453</v>
+        <v>0.0139353115592608</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.547298769439453</v>
+        <v>0.0139353115592608</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.0907120908170696</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B17" s="3" t="n">
         <v/>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4.515572542059796</v>
+        <v>0.013705561612471</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>4.515572542059796</v>
+        <v>0.013705561612471</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.0892756370314209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B18" s="3" t="n">
         <v/>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4.496367973833807</v>
+        <v>0.0131298098910866</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>4.496367973833807</v>
+        <v>0.0131298098910866</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.0872854262178332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B19" s="3" t="n">
         <v/>
       </c>
       <c r="C19" s="3" t="n">
-        <v>4.536788028537494</v>
+        <v>0.0122922461672396</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4.536788028537494</v>
+        <v>0.0122922461672396</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.08644021806113419</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B20" s="3" t="n">
         <v/>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.642481911391622</v>
+        <v>0.0115500822472932</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.642481911391622</v>
+        <v>0.0115500822472932</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.0881016067221644</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B21" s="3" t="n">
         <v/>
       </c>
       <c r="C21" s="3" t="n">
-        <v>4.741330241717404</v>
+        <v>0.0110588729642426</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>4.741330241717404</v>
+        <v>0.0110588729642426</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0.0909226006000606</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B22" s="3" t="n">
         <v/>
       </c>
       <c r="C22" s="3" t="n">
-        <v>4.808837227007343</v>
+        <v>0.0107471972434378</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>4.808837227007343</v>
+        <v>0.0107471972434378</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0.09419695416198751</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B23" s="3" t="n">
         <v/>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.755979040546843</v>
+        <v>0.0107236378482528</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.755979040546843</v>
+        <v>0.0107236378482528</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.0961520694055011</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B24" s="3" t="n">
         <v/>
       </c>
       <c r="C24" s="3" t="n">
-        <v>4.499557793437309</v>
+        <v>0.0106222736800593</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>4.499557793437309</v>
+        <v>0.0106222736800593</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.09511836386721551</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B25" s="3" t="n">
         <v/>
       </c>
       <c r="C25" s="3" t="n">
-        <v>4.499634493567239</v>
+        <v>0.0105947583078732</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>4.499634493567239</v>
+        <v>0.0105947583078732</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.08890036544307429</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B26" s="3" t="n">
         <v/>
       </c>
       <c r="C26" s="3" t="n">
-        <v>4.581150452828323</v>
+        <v>0.0100939172748274</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>4.581150452828323</v>
+        <v>0.0100939172748274</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>0.0898019203955526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B27" s="3" t="n">
         <v/>
       </c>
       <c r="C27" s="3" t="n">
-        <v>4.681444024458998</v>
+        <v>0.009911661582520799</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.681444024458998</v>
+        <v>0.009911661582520799</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.0925396639664454</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B28" s="3" t="n">
         <v/>
       </c>
       <c r="C28" s="3" t="n">
-        <v>4.739533602593766</v>
+        <v>0.009498278712500099</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>4.739533602593766</v>
+        <v>0.009498278712500099</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.09536156171078659</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B29" s="3" t="n">
         <v/>
       </c>
       <c r="C29" s="3" t="n">
-        <v>4.818530357607626</v>
+        <v>0.009238727622413401</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.818530357607626</v>
+        <v>0.009238727622413401</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.0976338953247966</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B30" s="3" t="n">
         <v/>
       </c>
       <c r="C30" s="3" t="n">
-        <v>4.91172090491929</v>
+        <v>0.0088870291813923</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.91172090491929</v>
+        <v>0.0088870291813923</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>0.1001045848513813</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B31" s="3" t="n">
         <v/>
       </c>
       <c r="C31" s="3" t="n">
-        <v>4.972763414689856</v>
+        <v>0.0085931121515957</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>4.972763414689856</v>
+        <v>0.0085931121515957</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0.101918903362487</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B32" s="3" t="n">
         <v/>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5.064385322566594</v>
+        <v>0.0083380370660362</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>5.064385322566594</v>
+        <v>0.0083380370660362</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.1032466368543564</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B33" s="3" t="n">
         <v/>
       </c>
       <c r="C33" s="3" t="n">
-        <v>5.119029358120903</v>
+        <v>0.008134945537045401</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>5.119029358120903</v>
+        <v>0.008134945537045401</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.1050771838478098</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B34" s="3" t="n">
         <v/>
       </c>
       <c r="C34" s="3" t="n">
-        <v>5.140999263264199</v>
+        <v>0.0077828906044046</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>5.140999263264199</v>
+        <v>0.0077828906044046</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.1065038069672278</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B35" s="3" t="n">
         <v/>
       </c>
       <c r="C35" s="3" t="n">
-        <v>4.985181376003024</v>
+        <v>0.0074925616124075</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>4.985181376003024</v>
+        <v>0.0074925616124075</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0.1074185276991728</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B36" s="3" t="n">
         <v/>
       </c>
       <c r="C36" s="3" t="n">
-        <v>5.125579342570314</v>
+        <v>0.0071259756178775</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>5.125579342570314</v>
+        <v>0.0071259756178775</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.1031417098147558</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B37" s="3" t="n">
         <v/>
       </c>
       <c r="C37" s="3" t="n">
-        <v>5.243292077004708</v>
+        <v>0.00649066658344</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>5.243292077004708</v>
+        <v>0.00649066658344</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.107865399191546</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B38" s="3" t="n">
         <v/>
       </c>
       <c r="C38" s="3" t="n">
-        <v>5.255120516328793</v>
+        <v>0.006097634312329</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>5.255120516328793</v>
+        <v>0.006097634312329</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0.1117669939642199</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0.0058474412415428</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0.0058474412415428</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0.1118533437167793</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>2024</v>
       </c>
-      <c r="B39" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>5.250680148824775</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>5.250680148824775</v>
+      <c r="B40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0.0055646997549548</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.0055646997549548</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0.1110803137719196</v>
       </c>
     </row>
   </sheetData>
@@ -1029,10 +1168,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1241,52 +1380,56 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S702-VAR-FROZEN77</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BLS CES + rebuilt 1977 BEA I-O (A and nominal X both frozen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S702 — Prices of Production (real, sector-disaggregated)</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t># S702 — Prices of Production (real, sector-disaggregated)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>## Series</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>## Series</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>- **SID**: S702</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- **Name**: Prices of Production (Chapter 7 series; real implementation per Ch4 §4.1 sector-disaggregated procedure)</t>
+          <t>- **SID**: S702</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1437,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>- **Chapter**: 7; registry `book_table` label "7.2" is project-internal. The classical price-of-production methodology lives in **Chapter 4 §4.1** (pp.78-88)</t>
+          <t>- **Name**: Prices of Production (Chapter 7 series; real implementation per Ch4 §4.1 sector-disaggregated procedure)</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1445,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- **Status**: validated_book_and_extension</t>
+          <t>- **Chapter**: 7; registry `book_table` label "7.2" is project-internal. The classical price-of-production methodology lives in **Chapter 4 §4.1** (pp.78-88)</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1453,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
+          <t>- **Status**: validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -1318,63 +1461,63 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- **Units**: labor-value units (sector pp*_j in hr-equivalent of producer-price gross output)</t>
+          <t>- **Status note**: (v1.1 Phase 4 — proxy:true retired)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>- **Units**: labor-value units (sector pp*_j in hr-equivalent of producer-price gross output)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>## Methodology — real implementation (v1.1 Phase 4)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>S702 implements the book's classical formula `pp*_j = (1 + r_bar)(c_j_labor + v_j_labor)` per ST 1994 Ch4 §4.1 (pp.81-83), with `c_j` and `v_j` constructed sector-by-sector via the matrix products quoted in p.81 and pp.81-82. The v1.0 scalar proxy `S701_proxy * (1 + r*)` has been retired (DIV-011); the real implementation works on sector vectors.</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S702 implements the book's classical formula `pp*_j = (1 + r_bar)(c_j_labor + v_j_labor)` per ST 1994 Ch4 §4.1 (pp.81-83), with `c_j` and `v_j` constructed sector-by-sector via the matrix products quoted in p.81 and pp.81-82. The v1.0 scalar proxy `S701_proxy * (1 + r*)` has been retired (DIV-011); the real implementation works on sector vectors.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Formula (per `Technical/code/P02_processors/P02_S702_prices_of_production.py`, v1.1 rewrite):</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Formula (per `Technical/code/P02_processors/P02_S702_prices_of_production.py`, v1.1 rewrite):</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>c_j_labor = sum_i lambda_i* * (M_p)_p,ij        # constant capital, labor-value units, per sector</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1525,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>v_j_labor = sum_i lambda_i* * (CONW_p)_p,ij     # variable capital, labor-value units, per sector</t>
+          <t>c_j_labor = sum_i lambda_i* * (M_p)_p,ij        # constant capital, labor-value units, per sector</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1533,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pp*_j     = (1 + r_bar) * (c_j_labor + v_j_labor)</t>
+          <t>v_j_labor = sum_i lambda_i* * (CONW_p)_p,ij     # variable capital, labor-value units, per sector</t>
         </is>
       </c>
     </row>
@@ -1398,63 +1541,63 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>pp*_j     = (1 + r_bar) * (c_j_labor + v_j_labor)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>where `lambda*_j` (hr/$) comes from real S701 (v1.1), `(M_p)_p,ij` is the producer-price component of input flows from sector i to sector j (from labeled BEA IO matrices filtered by Appendix F), `(CONW_p)_p,ij` is the producer-price component of the production-worker consumption basket (constructed from BLS CES production-worker compensation + BEA NIPA EC/WS ratio), and `r_bar` is the uniform Marxian rate of profit from S513.</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>where `lambda*_j` (hr/$) comes from real S701 (v1.1), `(M_p)_p,ij` is the producer-price component of input flows from sector i to sector j (from labeled BEA IO matrices filtered by Appendix F), `(CONW_p)_p,ij` is the producer-price component of the production-worker consumption basket (constructed from BLS CES production-worker compensation + BEA NIPA EC/WS ratio), and `r_bar` is the uniform Marxian rate of profit from S513.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>The book's verbatim methodological constraint (p.81) — that lambda*_j must be applied only to the producer-price components of commodity flows — is satisfied by construction. The Khanjian (1989) 6–9% S*/V* deviation envelope is now measurable for the first time via V03_S703.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>The book's verbatim methodological constraint (p.81) — that lambda*_j must be applied only to the producer-price components of commodity flows — is satisfied by construction. The Khanjian (1989) 6–9% S*/V* deviation envelope is now measurable for the first time via V03_S703.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>## Sources</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>## Sources</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>- **L01 + P02 (real implementation)**: `Technical/code/L01_loaders/L01_S702.py` (v1.1, loads real S701 lambda*, BLS CES wages, BEA NIPA EC tables, labeled IO matrices); `Technical/code/P02_processors/P02_S702_prices_of_production.py` (v1.1 rewrite, sector-disaggregated c/v construction and pp* aggregation)</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- **External data — real fetches**:</t>
+          <t>- **L01 + P02 (real implementation)**: `Technical/code/L01_loaders/L01_S702.py` (v1.1, loads real S701 lambda*, BLS CES wages, BEA NIPA EC tables, labeled IO matrices); `Technical/code/P02_processors/P02_S702_prices_of_production.py` (v1.1 rewrite, sector-disaggregated c/v construction and pp* aggregation)</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1605,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Real S701 lambda*_j vector (upstream, v1.1)</t>
+          <t>- **External data — real fetches**:</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1613,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BLS CES production-worker wages + employment + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/` (pulled 2026-05-24)</t>
+          <t xml:space="preserve">  - Real S701 lambda*_j vector (upstream, v1.1)</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1621,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BEA NIPA employee compensation tables (T10604 wages &amp; salaries by industry), cached at `Inputs/ST2/Inputs/API_Data/BEA/` (pulled 2026-02-24)</t>
+          <t xml:space="preserve">  - BLS CES production-worker wages + employment + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/` (pulled 2026-05-24)</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1629,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Labeled BEA IO matrices supplying (M_p)_p,ij producer-price input flows, at `Technical/data/intermediate/io_matrices_labeled/`</t>
+          <t xml:space="preserve">  - BEA NIPA employee compensation tables (T10604 wages &amp; salaries by industry), cached at `Inputs/ST2/Inputs/API_Data/BEA/` (pulled 2026-02-24)</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1637,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv`</t>
+          <t xml:space="preserve">  - Labeled BEA IO matrices supplying (M_p)_p,ij producer-price input flows, at `Technical/data/intermediate/io_matrices_labeled/`</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1645,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 — disaggregated c, v construction); `chunk_14/full_transcription.md` (Ch5 §5.3 + Appendix G — variable capital, ec and wp); `chunk_15/full_transcription.md` (Section 5.5 profit-rate measures); `chunk_31/full_transcription.md` (Appendix E Tables E.1 / E.2); `chunk_33/full_transcription.md` (Appendix G Tables G.1 / G.2)</t>
+          <t xml:space="preserve">  - Appendix F productive-share filter, at `Technical/data/source/appendix_F/Table_F_1.csv`</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1653,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- **Book tables**: Ch4 §4.1 equations pp.78-88 (sector-disaggregated procedure); Appendix E Tables E.1 (`C* = M'_p + Dp` annual 1948-1989), E.2 (constant capital components); Appendix G Tables G.1 / G.2 (variable capital, sectoral Lp)</t>
+          <t>- **KB chunks**: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_11/full_transcription.md` (Ch4 §4.1 — disaggregated c, v construction); `chunk_14/full_transcription.md` (Ch5 §5.3 + Appendix G — variable capital, ec and wp); `chunk_15/full_transcription.md` (Section 5.5 profit-rate measures); `chunk_31/full_transcription.md` (Appendix E Tables E.1 / E.2); `chunk_33/full_transcription.md` (Appendix G Tables G.1 / G.2)</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1661,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- **APIs**: BLS Public API v2; BEA API</t>
+          <t>- **Book tables**: Ch4 §4.1 equations pp.78-88 (sector-disaggregated procedure); Appendix E Tables E.1 (`C* = M'_p + Dp` annual 1948-1989), E.2 (constant capital components); Appendix G Tables G.1 / G.2 (variable capital, sectoral Lp)</t>
         </is>
       </c>
     </row>
@@ -1526,51 +1669,51 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- **Upstream series**: S401 (A-matrix), S402 (Leontief inverse B), S513 (Marxian profit rate r_bar), **S701 (real lambda* — v1.1)**</t>
+          <t>- **APIs**: BLS Public API v2; BEA API</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>- **Upstream series**: S401 (A-matrix), S402 (Leontief inverse B), S513 (Marxian profit rate r_bar), **S701 (real lambda* — v1.1)**</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>## Reference values</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Coordinator backfills from `Technical/chopped/S702.csv` after agents 1-3 commit L01/P02 rewrites and `O01_generate_chopped.py` regenerates chopped output. Expected magnitude: pp*_j is O((1+r_bar) * lambda*_j) with r_bar typically 0.4–0.6 in book period.</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Coordinator backfills from `Technical/chopped/S702.csv` after agents 1-3 commit L01/P02 rewrites and `O01_generate_chopped.py` regenerates chopped output. Expected magnitude: pp*_j is O((1+r_bar) * lambda*_j) with r_bar typically 0.4–0.6 in book period.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- Extension years (NAICS): 1997, 2002, 2007, 2012</t>
+          <t>- Six SIC benchmark years (book period): 1947, 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1721,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- Markup `pp*_j / lambda*_j ≈ 1 + r_bar` expected at all benchmark years (book finding qualitatively confirmed: prices systematically exceed labor values via profit-rate markup)</t>
+          <t>- Extension years (NAICS): 1997, 2002, 2007, 2012</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1729,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- **Khanjian benchmark**: 6–9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3 p.223) — now measurable for the first time via S703</t>
+          <t>- Markup `pp*_j / lambda*_j ≈ 1 + r_bar` expected at all benchmark years (book finding qualitatively confirmed: prices systematically exceed labor values via profit-rate markup)</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1737,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- 1948–1980 book aggregate finding: Marxian profit rate r* fell by almost a third, driven by C*/V* rising 77%</t>
+          <t>- **Khanjian benchmark**: 6–9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3 p.223) — now measurable for the first time via S703</t>
         </is>
       </c>
     </row>
@@ -1602,39 +1745,39 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- 1980–1989 book aggregate finding: r* partially recovered by ~7% of its 1948 value as the rate of surplus value accelerated</t>
+          <t>- 1948–1980 book aggregate finding: Marxian profit rate r* fell by almost a third, driven by C*/V* rising 77%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- 1980–1989 book aggregate finding: r* partially recovered by ~7% of its 1948 value as the rate of surplus value accelerated</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>## Known issues</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>## Known issues</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: same v1.1 null-factor stubs as S701; v1.2 follow-up sources non-null factors from BLS Employment Situation news-release archive.</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: applies to post-1997 extension arm; sector-mapping ambiguities documented.</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: same v1.1 null-factor stubs as S701; v1.2 follow-up sources non-null factors from BLS Employment Situation news-release archive.</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1785,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- **`λ_m` aggregation note**: the book Section 4.2 (pp.86-88) describes sector-level value-added decomposition; v1.1 implementation works on sector vectors throughout (per Ch4 §4.1 procedure) — the v1.0 single-scalar `λ_m` defect is fully addressed.</t>
+          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: applies to post-1997 extension arm; sector-mapping ambiguities documented.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1793,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- **Surplus accounting**: v1.1 uses VA*_j − V*_j per book Ch4 §4.1 (not the v1.0 GO_j − V*_j proxy error which misallocated depreciation).</t>
+          <t>- **`λ_m` aggregation note**: the book Section 4.2 (pp.86-88) describes sector-level value-added decomposition; v1.1 implementation works on sector vectors throughout (per Ch4 §4.1 procedure) — the v1.0 single-scalar `λ_m` defect is fully addressed.</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1801,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: may inherit from upstream S701 if the underlying labeled IO matrix has a 1963 gap; document via known_issues if observed in V03 rather than re-introducing proxy.</t>
+          <t>- **Surplus accounting**: v1.1 uses VA*_j − V*_j per book Ch4 §4.1 (not the v1.0 GO_j − V*_j proxy error which misallocated depreciation).</t>
         </is>
       </c>
     </row>
@@ -1666,39 +1809,39 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>- **Six SIC benchmark years only** for book period.</t>
+          <t>- **1963 benchmark anomaly (WARN-03)**: may inherit from upstream S701 if the underlying labeled IO matrix has a 1963 gap; document via known_issues if observed in V03 rather than re-introducing proxy.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- **Six SIC benchmark years only** for book period.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), **S701 (real lambda* — v1.1)**, S513 (Marxian profit rate), Appendix E Tables E.1 / E.2, Appendix G Tables G.1 / G.2, Appendix F productive-share filter</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- Downstream: S703 (consistent-procedure regression, now real)</t>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), **S701 (real lambda* — v1.1)**, S513 (Marxian profit rate), Appendix E Tables E.1 / E.2, Appendix G Tables G.1 / G.2, Appendix F productive-share filter</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1849,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- Related external: Khanjian (1989) 6–9% S*/V* benchmark; Wolff (1977b) symmetric-treatment biases; ST 1994 Ch7 §7.4 cross-study critique</t>
+          <t>- Downstream: S703 (consistent-procedure regression, now real)</t>
         </is>
       </c>
     </row>
@@ -1714,39 +1857,39 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S702_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
+          <t>- Related external: Khanjian (1989) 6–9% S*/V* benchmark; Wolff (1977b) symmetric-treatment biases; ST 1994 Ch7 §7.4 cross-study critique</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S702_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>## Provenance trail</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
         </is>
       </c>
     </row>
@@ -1754,13 +1897,21 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
@@ -2350,7 +2501,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>1997</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2513,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>ratio (1997 both-ways overlap; factor 0.858186 = sic_path 0.016091 / naics_path 0.018750)</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.2).", "extension_source": "Derived from extended S701 labor values + labeled BEA IO matrices (price-of-production identity)", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press., Chapter 7 (Table 7.2).", "extension_source": "Moving-benchmark extension, identical machinery to S701 (see S701 patch).", "note": "Extension block backfilled 2026-05-24 by doctor-cleanup pass to reflect actually-built extension data already present in chopped/&lt;sid&gt;.csv (validated_book_and_extension status). No substantive data change."}</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2594,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"1972": 5.347013, "1977": 2.810158, "2024": 5.25068}</t>
+          <t>{"1972": 0.070047, "1977": 0.047828, "1990": 0.020415, "2024": 0.005565}</t>
         </is>
       </c>
     </row>
@@ -2455,7 +2606,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[2.8102, 5.347]</t>
+          <t>[0.001, 1.0]</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2642,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Reference values from per-sector lambda_u = mean_j(hu*_j @ B) procedure in P02_S702 (v1.1 iter5, unchanged). 2024 EXT endpoint added per Decision 0008.</t>
+          <t>Pipeline regression snapshot on the REBUILT cache + corrected hours (WP-C v2.0). No book numeric anchor exists (same KB verification as S701). S702-A now also has a 1967 value (0.040276, 3 covered sectors) — previously NaN.</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S702.xlsx
+++ b/extenbooks/S702.xlsx
@@ -1621,7 +1621,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BLS CES production-worker wages + employment + weekly hours, cached at `Inputs/ST2/Inputs/API_Data/BLS/` (pulled 2026-05-24)</t>
+          <t xml:space="preserve">  - BLS CES production-worker wages + employment + weekly hours, cached at `data/raw/Inputs/API_Data/BLS/` (pulled 2026-05-24)</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - BEA NIPA employee compensation tables (T10604 wages &amp; salaries by industry), cached at `Inputs/ST2/Inputs/API_Data/BEA/` (pulled 2026-02-24)</t>
+          <t xml:space="preserve">  - BEA NIPA employee compensation tables (T10604 wages &amp; salaries by industry), cached at `data/raw/Inputs/API_Data/BEA/` (pulled 2026-02-24)</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `ST2/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Correct computation of S702 requires that c_j and v_j be expressed in labor-value units before computing pp*_j. The conversion scalar is λ_m = H_p / VA* (labor value of money = total productive hours / Marxian net value added). Money variable capital v_j (dollars per unit output) converts to v_j_labor = v_j × λ_m; money constant capital c_j converts to c_j_labor = c_j × λ_m. The initial ST2 implementation omitted this λ_m conversion, producing S702 values near floating-point zero at several benchmark years (most severely at 1963, WARN-03). After applying λ_m, the S702 series became numerically stable and the S703 regression MAD improved to 72–87%. The residual R² gap (0.70–0.98 vs. book's R² &gt; 0.95) traces to using a single aggregate λ_m scalar rather than sector-level value-added decomposition as required by ST 1994, Section 4.2 (pp. 86–88).</t>
+          <t>Correct computation of S702 requires that c_j and v_j be expressed in labor-value units before computing pp*_j. The conversion scalar is λ_m = H_p / VA* (labor value of money = total productive hours / Marxian net value added). Money variable capital v_j (dollars per unit output) converts to v_j_labor = v_j × λ_m; money constant capital c_j converts to c_j_labor = c_j × λ_m. The initial predecessor-build implementation omitted this λ_m conversion, producing S702 values near floating-point zero at several benchmark years (most severely at 1963, WARN-03). After applying λ_m, the S702 series became numerically stable and the S703 regression MAD improved to 72–87%. The residual R² gap (0.70–0.98 vs. book's R² &gt; 0.95) traces to using a single aggregate λ_m scalar rather than sector-level value-added decomposition as required by ST 1994, Section 4.2 (pp. 86–88).</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/extenbooks/S702.xlsx
+++ b/extenbooks/S702.xlsx
@@ -516,10 +516,10 @@
         <v>1967</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.040276449815129</v>
+        <v>0.0403</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.040276449815129</v>
+        <v>0.0403</v>
       </c>
       <c r="D3" s="3" t="n">
         <v/>
@@ -533,10 +533,10 @@
         <v>1972</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.0700467161716925</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.0700467161716925</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
@@ -550,10 +550,10 @@
         <v>1977</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0478280113031453</v>
+        <v>0.0478</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.0478280113031453</v>
+        <v>0.0478</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
@@ -570,13 +570,13 @@
         <v/>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.0204149045534999</v>
+        <v>0.0204</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0204149045534999</v>
+        <v>0.0204</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.06771158219096329</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="7">
@@ -587,13 +587,13 @@
         <v/>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.0192214288714607</v>
+        <v>0.0192</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0192214288714607</v>
+        <v>0.0192</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.0663052083414151</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v/>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.0182320148676809</v>
+        <v>0.0182</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0182320148676809</v>
+        <v>0.0182</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.06705737939711399</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +621,13 @@
         <v/>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.0178588025025679</v>
+        <v>0.0179</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0178588025025679</v>
+        <v>0.0179</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0693866735065774</v>
+        <v>0.0694</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v/>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.0175619841311453</v>
+        <v>0.0176</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.0175619841311453</v>
+        <v>0.0176</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0727791781949506</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="11">
@@ -655,13 +655,13 @@
         <v/>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.0171500938342048</v>
+        <v>0.0172</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.0171500938342048</v>
+        <v>0.0172</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.0754172029826658</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -672,13 +672,13 @@
         <v/>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.0165858027130644</v>
+        <v>0.0166</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.0165858027130644</v>
+        <v>0.0166</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.077970715818635</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="13">
@@ -689,13 +689,13 @@
         <v/>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.0160907931984493</v>
+        <v>0.0161</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.0160907931984493</v>
+        <v>0.0161</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0817524307630049</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="14">
@@ -706,13 +706,13 @@
         <v/>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.0154256321600575</v>
+        <v>0.0154</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.0154256321600575</v>
+        <v>0.0154</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.0851488822051715</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="15">
@@ -723,13 +723,13 @@
         <v/>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.0147148062694369</v>
+        <v>0.0147</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.0147148062694369</v>
+        <v>0.0147</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0882974684048997</v>
+        <v>0.0883</v>
       </c>
     </row>
     <row r="16">
@@ -740,13 +740,13 @@
         <v/>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.0139353115592608</v>
+        <v>0.0139</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.0139353115592608</v>
+        <v>0.0139</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.0907120908170696</v>
+        <v>0.0907</v>
       </c>
     </row>
     <row r="17">
@@ -757,13 +757,13 @@
         <v/>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.013705561612471</v>
+        <v>0.0137</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.013705561612471</v>
+        <v>0.0137</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.0892756370314209</v>
+        <v>0.0893</v>
       </c>
     </row>
     <row r="18">
@@ -774,13 +774,13 @@
         <v/>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.0131298098910866</v>
+        <v>0.0131</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.0131298098910866</v>
+        <v>0.0131</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.0872854262178332</v>
+        <v>0.0873</v>
       </c>
     </row>
     <row r="19">
@@ -791,13 +791,13 @@
         <v/>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.0122922461672396</v>
+        <v>0.0123</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.0122922461672396</v>
+        <v>0.0123</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.08644021806113419</v>
+        <v>0.0864</v>
       </c>
     </row>
     <row r="20">
@@ -808,13 +808,13 @@
         <v/>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.0115500822472932</v>
+        <v>0.0116</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.0115500822472932</v>
+        <v>0.0116</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0881016067221644</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="21">
@@ -825,13 +825,13 @@
         <v/>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.0110588729642426</v>
+        <v>0.0111</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.0110588729642426</v>
+        <v>0.0111</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.0909226006000606</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -842,13 +842,13 @@
         <v/>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.0107471972434378</v>
+        <v>0.0107</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.0107471972434378</v>
+        <v>0.0107</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.09419695416198751</v>
+        <v>0.09420000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -859,13 +859,13 @@
         <v/>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.0107236378482528</v>
+        <v>0.0107</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.0107236378482528</v>
+        <v>0.0107</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.0961520694055011</v>
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -876,13 +876,13 @@
         <v/>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.0106222736800593</v>
+        <v>0.0106</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.0106222736800593</v>
+        <v>0.0106</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.09511836386721551</v>
+        <v>0.0951</v>
       </c>
     </row>
     <row r="25">
@@ -893,13 +893,13 @@
         <v/>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.0105947583078732</v>
+        <v>0.0106</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.0105947583078732</v>
+        <v>0.0106</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.08890036544307429</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -910,13 +910,13 @@
         <v/>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.0100939172748274</v>
+        <v>0.0101</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.0100939172748274</v>
+        <v>0.0101</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.0898019203955526</v>
+        <v>0.0898</v>
       </c>
     </row>
     <row r="27">
@@ -927,13 +927,13 @@
         <v/>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.009911661582520799</v>
+        <v>0.00991</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.009911661582520799</v>
+        <v>0.00991</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0925396639664454</v>
+        <v>0.0925</v>
       </c>
     </row>
     <row r="28">
@@ -944,13 +944,13 @@
         <v/>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.009498278712500099</v>
+        <v>0.0095</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.009498278712500099</v>
+        <v>0.0095</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.09536156171078659</v>
+        <v>0.0954</v>
       </c>
     </row>
     <row r="29">
@@ -961,13 +961,13 @@
         <v/>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.009238727622413401</v>
+        <v>0.00924</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.009238727622413401</v>
+        <v>0.00924</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.0976338953247966</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         <v/>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.0088870291813923</v>
+        <v>0.00889</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.0088870291813923</v>
+        <v>0.00889</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.1001045848513813</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="31">
@@ -995,13 +995,13 @@
         <v/>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.0085931121515957</v>
+        <v>0.00859</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.0085931121515957</v>
+        <v>0.00859</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.101918903362487</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="32">
@@ -1012,13 +1012,13 @@
         <v/>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.0083380370660362</v>
+        <v>0.00834</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.0083380370660362</v>
+        <v>0.00834</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.1032466368543564</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="33">
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.008134945537045401</v>
+        <v>0.00813</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.008134945537045401</v>
+        <v>0.00813</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.1050771838478098</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="34">
@@ -1046,13 +1046,13 @@
         <v/>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.0077828906044046</v>
+        <v>0.00778</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.0077828906044046</v>
+        <v>0.00778</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.1065038069672278</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="35">
@@ -1063,13 +1063,13 @@
         <v/>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.0074925616124075</v>
+        <v>0.00749</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.0074925616124075</v>
+        <v>0.00749</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.1074185276991728</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="36">
@@ -1080,13 +1080,13 @@
         <v/>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0071259756178775</v>
+        <v>0.00713</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0071259756178775</v>
+        <v>0.00713</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.1031417098147558</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="37">
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.00649066658344</v>
+        <v>0.00649</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.00649066658344</v>
+        <v>0.00649</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.107865399191546</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="38">
@@ -1114,13 +1114,13 @@
         <v/>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.006097634312329</v>
+        <v>0.0061</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.006097634312329</v>
+        <v>0.0061</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.1117669939642199</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="39">
@@ -1131,13 +1131,13 @@
         <v/>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.0058474412415428</v>
+        <v>0.00585</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.0058474412415428</v>
+        <v>0.00585</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.1118533437167793</v>
+        <v>0.112</v>
       </c>
     </row>
     <row r="40">
@@ -1148,13 +1148,13 @@
         <v/>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.0055646997549548</v>
+        <v>0.00556</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.0055646997549548</v>
+        <v>0.00556</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.1110803137719196</v>
+        <v>0.111</v>
       </c>
     </row>
   </sheetData>
@@ -1168,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1637,7 +1637,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Labeled BEA IO matrices supplying (M_p)_p,ij producer-price input flows, at `Technical/data/intermediate/io_matrices_labeled/`</t>
+          <t xml:space="preserve">  - BEA IO matrices supplying the input flows. **[SUPERSEDED — WP-C v2.0 / F3 2026-07-07]** the published v2.0 engine reads the REBUILT cache `Technical/data/intermediate/io_matrices_rebuilt/` (via `utils.io_rebuilt`); the old defective labeled cache was retired to `Technical/MIGRATION/retired_io_20260707/io_matrices_labeled/`.</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>## Precision &amp; uncertainty (DIV-042) — Tier-A W1d, 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1777,39 +1777,31 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: same v1.1 null-factor stubs as S701; v1.2 follow-up sources non-null factors from BLS Employment Situation news-release archive.</t>
+          <t>Published S702 values (`data/final/S702.csv`, `chopped/S702.csv`, extenbook Data sheet) are reported to **3 significant figures** with an explicit uncertainty-band sidecar at `data/final/S702_LAMBDA_BAND.csv` (year, central, lo, hi, basis). Basis: **DIV-042** — the SIC-era per-sector gross output X_j entering both the hours-allocation weights and the coefficient denominator `hu*_j = hu_j/X_j` is *recovered* (X = II_IO + bucket-VA) with a measured median per-sector error of ~±11.5%. The F3 sensitivity propagation (`Handoffs/REVIEW_2026-07-07/F3_lambda_sensitivity_{aggregate,sector}.csv`, 2026-07-07) shows the published S702 aggregate is honest only to ±6.4–9.4% (independent-error Monte Carlo — little averaging: only 2–5 covered unproductive sectors) up to ±11.65% (worst-case common-mode); sector-level λ_j carries ±7–11%. The previous 15–17 displayed digits were false precision. The band uses the worst-case common-mode bound: `lo = central/1.115`, `hi = central/0.885` (λ ∝ 1/X, hence asymmetric). Rounding is applied ONLY at the P02 final-emit stage (`P02_S702_prices_of_production._round_sig`); `data/intermediate/S702.csv` retains full float64 precision for regression/reproducibility, and downstream S703 consumes the full-precision L01 panels, not the rounded published values.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: applies to post-1997 extension arm; sector-mapping ambiguities documented.</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>- **`λ_m` aggregation note**: the book Section 4.2 (pp.86-88) describes sector-level value-added decomposition; v1.1 implementation works on sector vectors throughout (per Ch4 §4.1 procedure) — the v1.0 single-scalar `λ_m` defect is fully addressed.</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>- **Surplus accounting**: v1.1 uses VA*_j − V*_j per book Ch4 §4.1 (not the v1.0 GO_j − V*_j proxy error which misallocated depreciation).</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>- **1963 benchmark anomaly (WARN-03)**: may inherit from upstream S701 if the underlying labeled IO matrix has a 1963 gap; document via known_issues if observed in V03 rather than re-introducing proxy.</t>
+          <t>- **BLS CES 2003 overhaul null bridge (DIV-010)**: same v1.1 null-factor stubs as S701; v1.2 follow-up sources non-null factors from BLS Employment Situation news-release archive.</t>
         </is>
       </c>
     </row>
@@ -1817,101 +1809,133 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>- **Six SIC benchmark years only** for book period.</t>
+          <t>- **SIC↔NAICS coarse concordance (DIV-008 reference)**: applies to post-1997 extension arm; sector-mapping ambiguities documented.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- **`λ_m` aggregation note**: the book Section 4.2 (pp.86-88) describes sector-level value-added decomposition; v1.1 implementation works on sector vectors throughout (per Ch4 §4.1 procedure) — the v1.0 single-scalar `λ_m` defect is fully addressed.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **Surplus accounting**: v1.1 uses VA*_j − V*_j per book Ch4 §4.1 (not the v1.0 GO_j − V*_j proxy error which misallocated depreciation).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- **1963 benchmark anomaly (WARN-03)**: may inherit from upstream S701 if the underlying labeled IO matrix has a 1963 gap; document via known_issues if observed in V03 rather than re-introducing proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), **S701 (real lambda* — v1.1)**, S513 (Marxian profit rate), Appendix E Tables E.1 / E.2, Appendix G Tables G.1 / G.2, Appendix F productive-share filter</t>
+          <t>- **Six SIC benchmark years only** for book period.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>- Downstream: S703 (consistent-procedure regression, now real)</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>- Related external: Khanjian (1989) 6–9% S*/V* benchmark; Wolff (1977b) symmetric-treatment biases; ST 1994 Ch7 §7.4 cross-study critique</t>
+          <t>## Cross-references</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S702_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>- Upstream: S401 (A-matrix), S402 (Leontief inverse B), **S701 (real lambda* — v1.1)**, S513 (Marxian profit rate), Appendix E Tables E.1 / E.2, Appendix G Tables G.1 / G.2, Appendix F productive-share filter</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- Downstream: S703 (consistent-procedure regression, now real)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>- Related external: Khanjian (1989) 6–9% S*/V* benchmark; Wolff (1977b) symmetric-treatment biases; ST 1994 Ch7 §7.4 cross-study critique</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+          <t>- Project artifacts: `Technical/Handoffs/CH7_REAL_FIX_PLAN.md`; `Technical/_v1.1_patches/S702_ch7_realfix_patch.json`; `Technical/_v1.1_patches/DIVERGENCE_REGISTER_DIV011_patch.json`</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+          <t>## Provenance trail</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/S702_research.json`, researcher `agent`, 2026-05-06; ported from `predecessor-build/research/T702_research.json` on 2026-05-14; verbatim quotes backfilled 2026-05-19 and 2026-05-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>- **DPR v1.0**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (proxy disclosure version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>- **DPR v1.1 (this version)**: 2026-05-24, v1.1 Phase 4 iteration 5 Ch7 real-fix agent 4. Real implementation replaces proxy disclosure. See DIV-011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 5 EXECUTION (Ch7 real-fix sub-stage); doctor gate IDs P13/P31/P36</t>
         </is>
